--- a/tests/comethyl_output/09a_me_trait_analysis/cov3_75pct/covMin4_methSD0p08/v1_all_pcs/ME_Trait_Correlations_Bicor.xlsx
+++ b/tests/comethyl_output/09a_me_trait_analysis/cov3_75pct/covMin4_methSD0p08/v1_all_pcs/ME_Trait_Correlations_Bicor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t xml:space="preserve">module</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">p</t>
   </si>
   <si>
-    <t xml:space="preserve">blue</t>
+    <t xml:space="preserve">turquoise</t>
   </si>
   <si>
     <t xml:space="preserve">SequencingNumber</t>
@@ -235,9 +235,6 @@
   </si>
   <si>
     <t xml:space="preserve">soc_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turquoise</t>
   </si>
   <si>
     <t xml:space="preserve">grey</t>
@@ -600,19 +597,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
-        <v>0.100343436594376</v>
+        <v>0.0218656313419788</v>
       </c>
       <c r="E2" t="n">
-        <v>0.690242836178421</v>
+        <v>0.148323568186249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.691409583286705</v>
+        <v>0.148335391298072</v>
       </c>
       <c r="G2" t="n">
-        <v>0.492709452130228</v>
+        <v>0.882726436727687</v>
       </c>
     </row>
     <row r="3">
@@ -623,19 +620,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.235038362737351</v>
+        <v>-0.0269389243934811</v>
       </c>
       <c r="E3" t="n">
-        <v>1.17338305515141</v>
+        <v>-0.129225808828593</v>
       </c>
       <c r="F3" t="n">
-        <v>1.18463435207698</v>
+        <v>0.129241446945556</v>
       </c>
       <c r="G3" t="n">
-        <v>0.247761124372667</v>
+        <v>0.898290174688631</v>
       </c>
     </row>
     <row r="4">
@@ -646,19 +643,19 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.176080983624414</v>
+        <v>-0.158452858379838</v>
       </c>
       <c r="E4" t="n">
-        <v>0.871701741426657</v>
+        <v>-0.766370563738701</v>
       </c>
       <c r="F4" t="n">
-        <v>0.876308853027503</v>
+        <v>0.76963638073927</v>
       </c>
       <c r="G4" t="n">
-        <v>0.389549176287345</v>
+        <v>0.449348308898074</v>
       </c>
     </row>
     <row r="5">
@@ -669,19 +666,19 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.176080983624414</v>
+        <v>0.158452858379838</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.871701741426656</v>
+        <v>0.766370563738699</v>
       </c>
       <c r="F5" t="n">
-        <v>0.876308853027503</v>
+        <v>0.769636380739267</v>
       </c>
       <c r="G5" t="n">
-        <v>0.389549176287346</v>
+        <v>0.449348308898076</v>
       </c>
     </row>
     <row r="6">
@@ -692,19 +689,19 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.176080983624414</v>
+        <v>-0.158452858379838</v>
       </c>
       <c r="E6" t="n">
-        <v>0.871701741426657</v>
+        <v>-0.766370563738701</v>
       </c>
       <c r="F6" t="n">
-        <v>0.876308853027503</v>
+        <v>0.76963638073927</v>
       </c>
       <c r="G6" t="n">
-        <v>0.389549176287345</v>
+        <v>0.449348308898074</v>
       </c>
     </row>
     <row r="7">
@@ -715,19 +712,19 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.12945727339917</v>
+        <v>0.00514959267308769</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.892522817843189</v>
+        <v>0.0349265455206739</v>
       </c>
       <c r="F7" t="n">
-        <v>0.895046164442782</v>
+        <v>0.0349266998890699</v>
       </c>
       <c r="G7" t="n">
-        <v>0.37532344831376</v>
+        <v>0.972289312869394</v>
       </c>
     </row>
     <row r="8">
@@ -738,19 +735,19 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.150608029429696</v>
+        <v>0.0404928435878421</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.04043141190324</v>
+        <v>0.274786079090922</v>
       </c>
       <c r="F8" t="n">
-        <v>1.04442985919378</v>
+        <v>0.274861260548861</v>
       </c>
       <c r="G8" t="n">
-        <v>0.301628784713979</v>
+        <v>0.784653607395666</v>
       </c>
     </row>
     <row r="9">
@@ -761,19 +758,19 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.131394544374795</v>
+        <v>0.0078912577789932</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.906033919272146</v>
+        <v>0.0535222252352515</v>
       </c>
       <c r="F9" t="n">
-        <v>0.908673673664425</v>
+        <v>0.0535227807489262</v>
       </c>
       <c r="G9" t="n">
-        <v>0.368158479806467</v>
+        <v>0.957547154546712</v>
       </c>
     </row>
     <row r="10">
@@ -784,19 +781,19 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0788054773683309</v>
+        <v>-0.0152830122209548</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.541385718692399</v>
+        <v>-0.103662503354361</v>
       </c>
       <c r="F10" t="n">
-        <v>0.541948586865397</v>
+        <v>0.103666539446462</v>
       </c>
       <c r="G10" t="n">
-        <v>0.590414192388787</v>
+        <v>0.917884639553836</v>
       </c>
     </row>
     <row r="11">
@@ -807,19 +804,19 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0814233468805653</v>
+        <v>-0.0116834429474552</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.559448873530125</v>
+        <v>-0.0792445712429049</v>
       </c>
       <c r="F11" t="n">
-        <v>0.560069995233428</v>
+        <v>0.0792463742707846</v>
       </c>
       <c r="G11" t="n">
-        <v>0.578091560395053</v>
+        <v>0.937180405656177</v>
       </c>
     </row>
     <row r="12">
@@ -830,19 +827,19 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.13036215874671</v>
+        <v>0.0544126097052737</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.898832891880128</v>
+        <v>0.369409136381631</v>
       </c>
       <c r="F12" t="n">
-        <v>0.90141016839528</v>
+        <v>0.369591811010442</v>
       </c>
       <c r="G12" t="n">
-        <v>0.371966428806115</v>
+        <v>0.713382715650216</v>
       </c>
     </row>
     <row r="13">
@@ -853,19 +850,19 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.139570706872242</v>
+        <v>0.0998764627073316</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.952834125782075</v>
+        <v>0.672232900464953</v>
       </c>
       <c r="F13" t="n">
-        <v>0.955971536646577</v>
+        <v>0.673358576933755</v>
       </c>
       <c r="G13" t="n">
-        <v>0.344083880168325</v>
+        <v>0.504163026969011</v>
       </c>
     </row>
     <row r="14">
@@ -876,19 +873,19 @@
         <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0154299195644397</v>
+        <v>0.00426150694518082</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.105790595205756</v>
+        <v>0.0289031212929238</v>
       </c>
       <c r="F14" t="n">
-        <v>0.105794793735597</v>
+        <v>0.0289032087763032</v>
       </c>
       <c r="G14" t="n">
-        <v>0.916195418039798</v>
+        <v>0.97706682249641</v>
       </c>
     </row>
     <row r="15">
@@ -899,19 +896,19 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>0.142060814725952</v>
+        <v>-0.166129153102091</v>
       </c>
       <c r="E15" t="n">
-        <v>0.980552020548141</v>
+        <v>-1.13728346036627</v>
       </c>
       <c r="F15" t="n">
-        <v>0.983898645288399</v>
+        <v>1.1426205885672</v>
       </c>
       <c r="G15" t="n">
-        <v>0.330203369884036</v>
+        <v>0.259108587591894</v>
       </c>
     </row>
     <row r="16">
@@ -922,19 +919,19 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>0.221440143139011</v>
+        <v>0.0055019365895487</v>
       </c>
       <c r="E16" t="n">
-        <v>1.54368778408328</v>
+        <v>0.0373163260375675</v>
       </c>
       <c r="F16" t="n">
-        <v>1.55676544874946</v>
+        <v>0.0373165143106408</v>
       </c>
       <c r="G16" t="n">
-        <v>0.126234986678619</v>
+        <v>0.970394115081314</v>
       </c>
     </row>
     <row r="17">
@@ -945,19 +942,19 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
-        <v>0.346905454726616</v>
+        <v>0.0471139425589694</v>
       </c>
       <c r="E17" t="n">
-        <v>2.42784349659265</v>
+        <v>0.312750083104914</v>
       </c>
       <c r="F17" t="n">
-        <v>2.48119445253468</v>
+        <v>0.312865970618884</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0168974109969343</v>
+        <v>0.755860652690403</v>
       </c>
     </row>
     <row r="18">
@@ -968,19 +965,19 @@
         <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0553350438544964</v>
+        <v>-0.0616496009574505</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.332349755218872</v>
+        <v>-0.365187079961592</v>
       </c>
       <c r="F18" t="n">
-        <v>0.332519735664769</v>
+        <v>0.365419038122934</v>
       </c>
       <c r="G18" t="n">
-        <v>0.741425408498674</v>
+        <v>0.71699781459591</v>
       </c>
     </row>
     <row r="19">
@@ -991,19 +988,19 @@
         <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0697697550633987</v>
+        <v>-0.0649616139976527</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.441980769656694</v>
+        <v>-0.406257263990235</v>
       </c>
       <c r="F19" t="n">
-        <v>0.442340605918874</v>
+        <v>0.406543866147634</v>
       </c>
       <c r="G19" t="n">
-        <v>0.660625407188164</v>
+        <v>0.686565455384381</v>
       </c>
     </row>
     <row r="20">
@@ -1014,19 +1011,19 @@
         <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0510039049229114</v>
+        <v>-0.041119288921712</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.293249590018534</v>
+        <v>-0.232737053754329</v>
       </c>
       <c r="F20" t="n">
-        <v>0.293376970720314</v>
+        <v>0.232802718478531</v>
       </c>
       <c r="G20" t="n">
-        <v>0.771071163042564</v>
+        <v>0.817397253535461</v>
       </c>
     </row>
     <row r="21">
@@ -1037,19 +1034,19 @@
         <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0580435201927723</v>
+        <v>-0.213570325079777</v>
       </c>
       <c r="E21" t="n">
-        <v>0.367512548644</v>
+        <v>-1.35459837068021</v>
       </c>
       <c r="F21" t="n">
-        <v>0.36771940963383</v>
+        <v>1.36524561947555</v>
       </c>
       <c r="G21" t="n">
-        <v>0.71502111952338</v>
+        <v>0.179999821325395</v>
       </c>
     </row>
     <row r="22">
@@ -1063,16 +1060,16 @@
         <v>29</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0943560379883632</v>
+        <v>-0.0402996115438976</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.491751200182662</v>
+        <v>-0.209516395628701</v>
       </c>
       <c r="F22" t="n">
-        <v>0.492485571577474</v>
+        <v>0.209573172875887</v>
       </c>
       <c r="G22" t="n">
-        <v>0.626357189439056</v>
+        <v>0.835574123178056</v>
       </c>
     </row>
     <row r="23">
@@ -1083,19 +1080,19 @@
         <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0383778028049161</v>
+        <v>-0.238192597272926</v>
       </c>
       <c r="E23" t="n">
-        <v>0.236692915530238</v>
+        <v>-1.47724219289909</v>
       </c>
       <c r="F23" t="n">
-        <v>0.236751079353313</v>
+        <v>1.4918062633532</v>
       </c>
       <c r="G23" t="n">
-        <v>0.814121550702674</v>
+        <v>0.144227754123156</v>
       </c>
     </row>
     <row r="24">
@@ -1106,19 +1103,19 @@
         <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.107693346392864</v>
+        <v>-0.0275558206186178</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.657623303497002</v>
+        <v>-0.165376790338079</v>
       </c>
       <c r="F24" t="n">
-        <v>0.658905139348971</v>
+        <v>0.16539773080794</v>
       </c>
       <c r="G24" t="n">
-        <v>0.514036628136376</v>
+        <v>0.86955627018892</v>
       </c>
     </row>
     <row r="25">
@@ -1129,19 +1126,19 @@
         <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>0.290555550987982</v>
+        <v>0.00865980642884621</v>
       </c>
       <c r="E25" t="n">
-        <v>2.00691304819843</v>
+        <v>0.0574440933457844</v>
       </c>
       <c r="F25" t="n">
-        <v>2.03698525244695</v>
+        <v>0.0574448113613172</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0475594739120552</v>
+        <v>0.954450954994043</v>
       </c>
     </row>
     <row r="26">
@@ -1152,19 +1149,19 @@
         <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.000885818487035575</v>
+        <v>0.0604407582660066</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.00560240949038931</v>
+        <v>0.37791304640243</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00560241022306785</v>
+        <v>0.378143742005234</v>
       </c>
       <c r="G26" t="n">
-        <v>0.995557795162986</v>
+        <v>0.707374318087881</v>
       </c>
     </row>
     <row r="27">
@@ -1175,19 +1172,19 @@
         <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0968129101011407</v>
+        <v>0.00686910501400955</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.574552452380999</v>
+        <v>0.0400540508834292</v>
       </c>
       <c r="F27" t="n">
-        <v>0.575456048919318</v>
+        <v>0.0400543658831679</v>
       </c>
       <c r="G27" t="n">
-        <v>0.568664472626849</v>
+        <v>0.968284065466096</v>
       </c>
     </row>
     <row r="28">
@@ -1198,19 +1195,19 @@
         <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.222455363006946</v>
+        <v>-0.00656442624164039</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.33844103589415</v>
+        <v>-0.0382774034512756</v>
       </c>
       <c r="F28" t="n">
-        <v>1.34988798638406</v>
+        <v>0.0382776783661112</v>
       </c>
       <c r="G28" t="n">
-        <v>0.185718088822263</v>
+        <v>0.969690162472812</v>
       </c>
     </row>
     <row r="29">
@@ -1221,19 +1218,19 @@
         <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.157589699806204</v>
+        <v>0.0581962358131105</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.992417891210121</v>
+        <v>0.359151516147344</v>
       </c>
       <c r="F29" t="n">
-        <v>0.996600201572077</v>
+        <v>0.359354738734098</v>
       </c>
       <c r="G29" t="n">
-        <v>0.325102140094016</v>
+        <v>0.721319007669304</v>
       </c>
     </row>
     <row r="30">
@@ -1244,19 +1241,19 @@
         <v>36</v>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.286578288905961</v>
+        <v>0.0699663973283794</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.81748123710173</v>
+        <v>0.426285488416534</v>
       </c>
       <c r="F30" t="n">
-        <v>1.84392738170396</v>
+        <v>0.426634512438819</v>
       </c>
       <c r="G30" t="n">
-        <v>0.073001637522175</v>
+        <v>0.672117743588307</v>
       </c>
     </row>
     <row r="31">
@@ -1267,19 +1264,19 @@
         <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.150977378971701</v>
+        <v>-0.0479312830257302</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.860636421479463</v>
+        <v>-0.267074741487623</v>
       </c>
       <c r="F31" t="n">
-        <v>0.863960417885368</v>
+        <v>0.267177173444552</v>
       </c>
       <c r="G31" t="n">
-        <v>0.394039652093021</v>
+        <v>0.791102223403222</v>
       </c>
     </row>
     <row r="32">
@@ -1290,19 +1287,19 @@
         <v>38</v>
       </c>
       <c r="C32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.236091931447143</v>
+        <v>0.0484594261347849</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.31799180272093</v>
+        <v>0.261166558240276</v>
       </c>
       <c r="F32" t="n">
-        <v>1.33074804890776</v>
+        <v>0.261268947528027</v>
       </c>
       <c r="G32" t="n">
-        <v>0.193298576947118</v>
+        <v>0.795731716571749</v>
       </c>
     </row>
     <row r="33">
@@ -1313,19 +1310,19 @@
         <v>39</v>
       </c>
       <c r="C33" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00202048771763972</v>
+        <v>-0.195669826851809</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0126179589228622</v>
+        <v>-1.2219470805074</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0126179675080848</v>
+        <v>1.22996525597148</v>
       </c>
       <c r="G33" t="n">
-        <v>0.989996913772561</v>
+        <v>0.226270729912235</v>
       </c>
     </row>
     <row r="34">
@@ -1336,19 +1333,19 @@
         <v>40</v>
       </c>
       <c r="C34" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.156414218087424</v>
+        <v>-0.0787645503374036</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.984891486290487</v>
+        <v>-0.486545118696903</v>
       </c>
       <c r="F34" t="n">
-        <v>0.988979283726069</v>
+        <v>0.487050442535219</v>
       </c>
       <c r="G34" t="n">
-        <v>0.328769695680072</v>
+        <v>0.629020381304059</v>
       </c>
     </row>
     <row r="35">
@@ -1362,16 +1359,16 @@
         <v>28</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0681982255766484</v>
+        <v>0.00529739890931065</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.348284711497034</v>
+        <v>0.0270117930839821</v>
       </c>
       <c r="F35" t="n">
-        <v>0.348555593369616</v>
+        <v>0.0270119194226384</v>
       </c>
       <c r="G35" t="n">
-        <v>0.730229678185737</v>
+        <v>0.978656492803771</v>
       </c>
     </row>
     <row r="36">
@@ -1385,16 +1382,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.126281408022094</v>
+        <v>-0.0408955292705587</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.647367308516028</v>
+        <v>-0.208643468550377</v>
       </c>
       <c r="F36" t="n">
-        <v>0.649107823229524</v>
+        <v>0.208701695781771</v>
       </c>
       <c r="G36" t="n">
-        <v>0.521961821508407</v>
+        <v>0.836307541529726</v>
       </c>
     </row>
     <row r="37">
@@ -1405,19 +1402,19 @@
         <v>43</v>
       </c>
       <c r="C37" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0201026414783654</v>
+        <v>-0.190314530050186</v>
       </c>
       <c r="E37" t="n">
-        <v>0.12393770150284</v>
+        <v>-1.17192631448883</v>
       </c>
       <c r="F37" t="n">
-        <v>0.123946051459928</v>
+        <v>1.17918994830291</v>
       </c>
       <c r="G37" t="n">
-        <v>0.902011304298081</v>
+        <v>0.245849746387376</v>
       </c>
     </row>
     <row r="38">
@@ -1428,19 +1425,19 @@
         <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.116957838763811</v>
+        <v>-0.0185592945120233</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.714697547598641</v>
+        <v>-0.111368555117085</v>
       </c>
       <c r="F38" t="n">
-        <v>0.716343107410705</v>
+        <v>0.111374950130882</v>
       </c>
       <c r="G38" t="n">
-        <v>0.478276822717124</v>
+        <v>0.911937681096365</v>
       </c>
     </row>
     <row r="39">
@@ -1451,19 +1448,19 @@
         <v>45</v>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.293734356170432</v>
+        <v>-0.0110307154974187</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.60146462312182</v>
+        <v>-0.0573196039513246</v>
       </c>
       <c r="F39" t="n">
-        <v>1.62602480234952</v>
+        <v>0.0573207664625916</v>
       </c>
       <c r="G39" t="n">
-        <v>0.115148402695224</v>
+        <v>0.954711790072889</v>
       </c>
     </row>
     <row r="40">
@@ -1474,19 +1471,19 @@
         <v>46</v>
       </c>
       <c r="C40" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0945342295957658</v>
+        <v>0.127789801735788</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.544684252788857</v>
+        <v>0.72686227211015</v>
       </c>
       <c r="F40" t="n">
-        <v>0.54550076839391</v>
+        <v>0.728864039740806</v>
       </c>
       <c r="G40" t="n">
-        <v>0.589077729081641</v>
+        <v>0.471385900057094</v>
       </c>
     </row>
     <row r="41">
@@ -1497,19 +1494,19 @@
         <v>47</v>
       </c>
       <c r="C41" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.00411683257444398</v>
+        <v>-0.395589783045375</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0221699471450426</v>
+        <v>-2.21401563814101</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0221700097696608</v>
+        <v>2.27918350394534</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9824641845209</v>
+        <v>0.0304790566043085</v>
       </c>
     </row>
     <row r="42">
@@ -1520,19 +1517,19 @@
         <v>48</v>
       </c>
       <c r="C42" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D42" t="n">
-        <v>0.300738981336516</v>
+        <v>-0.132970516045055</v>
       </c>
       <c r="E42" t="n">
-        <v>1.67118826307247</v>
+        <v>-0.707805293393127</v>
       </c>
       <c r="F42" t="n">
-        <v>1.69814193248856</v>
+        <v>0.709917909847822</v>
       </c>
       <c r="G42" t="n">
-        <v>0.100187834296182</v>
+        <v>0.483625888839135</v>
       </c>
     </row>
     <row r="43">
@@ -1546,16 +1543,16 @@
         <v>15</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0823554833015958</v>
+        <v>-0.233690228490742</v>
       </c>
       <c r="E43" t="n">
-        <v>0.297610980582054</v>
+        <v>-0.858443275043694</v>
       </c>
       <c r="F43" t="n">
-        <v>0.297949045571149</v>
+        <v>0.866576654879853</v>
       </c>
       <c r="G43" t="n">
-        <v>0.770450507781942</v>
+        <v>0.401885583009214</v>
       </c>
     </row>
     <row r="44">
@@ -1569,16 +1566,16 @@
         <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0616626644301904</v>
+        <v>-0.000585012597874485</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.289590941617946</v>
+        <v>-0.00274395262179585</v>
       </c>
       <c r="F44" t="n">
-        <v>0.289774961082629</v>
+        <v>0.00274395277831061</v>
       </c>
       <c r="G44" t="n">
-        <v>0.77470192160478</v>
+        <v>0.997835375071684</v>
       </c>
     </row>
     <row r="45">
@@ -1589,19 +1586,19 @@
         <v>51</v>
       </c>
       <c r="C45" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0934575188575253</v>
+        <v>-0.0181989464629368</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.487040819080092</v>
+        <v>-0.092807029993657</v>
       </c>
       <c r="F45" t="n">
-        <v>0.487754282714425</v>
+        <v>0.0928121541835917</v>
       </c>
       <c r="G45" t="n">
-        <v>0.629661216444032</v>
+        <v>0.926764273577948</v>
       </c>
     </row>
     <row r="46">
@@ -1612,19 +1609,19 @@
         <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0382328976473405</v>
+        <v>0.187917585509881</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.219738385316095</v>
+        <v>1.07580723161134</v>
       </c>
       <c r="F46" t="n">
-        <v>0.219791975391602</v>
+        <v>1.0823038518906</v>
       </c>
       <c r="G46" t="n">
-        <v>0.827387142751826</v>
+        <v>0.287206138530235</v>
       </c>
     </row>
     <row r="47">
@@ -1635,19 +1632,19 @@
         <v>53</v>
       </c>
       <c r="C47" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0196677560360497</v>
+        <v>-0.219707606308033</v>
       </c>
       <c r="E47" t="n">
-        <v>0.10220983849359</v>
+        <v>-1.13886021815536</v>
       </c>
       <c r="F47" t="n">
-        <v>0.102216429799883</v>
+        <v>1.14835248281043</v>
       </c>
       <c r="G47" t="n">
-        <v>0.919340258928435</v>
+        <v>0.26127909277735</v>
       </c>
     </row>
     <row r="48">
@@ -1658,19 +1655,19 @@
         <v>54</v>
       </c>
       <c r="C48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D48" t="n">
-        <v>0.18877514445837</v>
+        <v>-0.0488484174634846</v>
       </c>
       <c r="E48" t="n">
-        <v>0.992811937265448</v>
+        <v>-0.249277432777317</v>
       </c>
       <c r="F48" t="n">
-        <v>0.998863654822348</v>
+        <v>0.249376738937399</v>
       </c>
       <c r="G48" t="n">
-        <v>0.326729103637296</v>
+        <v>0.805029002504228</v>
       </c>
     </row>
     <row r="49">
@@ -1684,16 +1681,16 @@
         <v>15</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00000601220986317513</v>
+        <v>-0.221555769433474</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000021677330940737</v>
+        <v>-0.812300405816266</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0000216773309409201</v>
+        <v>0.819189426685451</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9999830331105</v>
+        <v>0.427441515585518</v>
       </c>
     </row>
     <row r="50">
@@ -1707,16 +1704,16 @@
         <v>23</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.110363637544528</v>
+        <v>-0.0573758115327461</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.507818227197674</v>
+        <v>-0.263218089963434</v>
       </c>
       <c r="F50" t="n">
-        <v>0.508858197558735</v>
+        <v>0.263362849870776</v>
       </c>
       <c r="G50" t="n">
-        <v>0.616156489429332</v>
+        <v>0.794837780223629</v>
       </c>
     </row>
     <row r="51">
@@ -1727,19 +1724,19 @@
         <v>57</v>
       </c>
       <c r="C51" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.227046660814935</v>
+        <v>0.11083875261509</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.42443206838639</v>
+        <v>0.676987267052813</v>
       </c>
       <c r="F51" t="n">
-        <v>1.43714219164777</v>
+        <v>0.67838575104301</v>
       </c>
       <c r="G51" t="n">
-        <v>0.158861182927465</v>
+        <v>0.501748237527752</v>
       </c>
     </row>
     <row r="52">
@@ -1750,19 +1747,19 @@
         <v>58</v>
       </c>
       <c r="C52" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.16420862828041</v>
+        <v>0.00803858201069772</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.00796794736929</v>
+        <v>0.048232530991525</v>
       </c>
       <c r="F52" t="n">
-        <v>1.01258732478282</v>
+        <v>0.0482330504703011</v>
       </c>
       <c r="G52" t="n">
-        <v>0.317833558875949</v>
+        <v>0.961797111095994</v>
       </c>
     </row>
     <row r="53">
@@ -1773,19 +1770,19 @@
         <v>59</v>
       </c>
       <c r="C53" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D53" t="n">
-        <v>0.141301357097082</v>
+        <v>-0.205806537704615</v>
       </c>
       <c r="E53" t="n">
-        <v>0.853519183111736</v>
+        <v>-1.23520901283368</v>
       </c>
       <c r="F53" t="n">
-        <v>0.856400728841735</v>
+        <v>1.24420292440414</v>
       </c>
       <c r="G53" t="n">
-        <v>0.397440969116028</v>
+        <v>0.221693036930003</v>
       </c>
     </row>
     <row r="54">
@@ -1796,19 +1793,19 @@
         <v>60</v>
       </c>
       <c r="C54" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>0.165888058418102</v>
+        <v>-0.121652944666871</v>
       </c>
       <c r="E54" t="n">
-        <v>0.990561012291359</v>
+        <v>-0.712883212990999</v>
       </c>
       <c r="F54" t="n">
-        <v>0.995195835148687</v>
+        <v>0.714660467250534</v>
       </c>
       <c r="G54" t="n">
-        <v>0.326471961917773</v>
+        <v>0.479697336976608</v>
       </c>
     </row>
     <row r="55">
@@ -1819,19 +1816,19 @@
         <v>61</v>
       </c>
       <c r="C55" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.0788649578938964</v>
+        <v>-0.0361412848408642</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.541796046817074</v>
+        <v>-0.245228929081154</v>
       </c>
       <c r="F55" t="n">
-        <v>0.542360196057516</v>
+        <v>0.245282365138953</v>
       </c>
       <c r="G55" t="n">
-        <v>0.590132915658312</v>
+        <v>0.807328820785319</v>
       </c>
     </row>
     <row r="56">
@@ -1842,19 +1839,19 @@
         <v>62</v>
       </c>
       <c r="C56" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D56" t="n">
-        <v>0.228789775859295</v>
+        <v>0.174397035097201</v>
       </c>
       <c r="E56" t="n">
-        <v>1.43576612149138</v>
+        <v>1.0717710403568</v>
       </c>
       <c r="F56" t="n">
-        <v>1.44878261966432</v>
+        <v>1.07732531313773</v>
       </c>
       <c r="G56" t="n">
-        <v>0.155600622142963</v>
+        <v>0.288309119591505</v>
       </c>
     </row>
     <row r="57">
@@ -1865,19 +1862,19 @@
         <v>63</v>
       </c>
       <c r="C57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D57" t="n">
-        <v>0.228698917623884</v>
+        <v>0.180731313843282</v>
       </c>
       <c r="E57" t="n">
-        <v>1.43517510962122</v>
+        <v>1.11155546879448</v>
       </c>
       <c r="F57" t="n">
-        <v>1.44817551124287</v>
+        <v>1.11775224117825</v>
       </c>
       <c r="G57" t="n">
-        <v>0.155769361880036</v>
+        <v>0.270878149495775</v>
       </c>
     </row>
     <row r="58">
@@ -1891,16 +1888,16 @@
         <v>40</v>
       </c>
       <c r="D58" t="n">
-        <v>0.206988495211717</v>
+        <v>0.171900353517508</v>
       </c>
       <c r="E58" t="n">
-        <v>1.29466859845936</v>
+        <v>1.07029160627569</v>
       </c>
       <c r="F58" t="n">
-        <v>1.30420750898558</v>
+        <v>1.07567710697255</v>
       </c>
       <c r="G58" t="n">
-        <v>0.200007658898337</v>
+        <v>0.288854128029045</v>
       </c>
     </row>
     <row r="59">
@@ -1914,16 +1911,16 @@
         <v>40</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0492155758195051</v>
+        <v>0.293176283060195</v>
       </c>
       <c r="E59" t="n">
-        <v>0.303630491808333</v>
+        <v>1.86188546026478</v>
       </c>
       <c r="F59" t="n">
-        <v>0.303753279259362</v>
+        <v>1.89032383568471</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7629728937195</v>
+        <v>0.0663592393733625</v>
       </c>
     </row>
     <row r="60">
@@ -1934,19 +1931,19 @@
         <v>66</v>
       </c>
       <c r="C60" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.0188956220254383</v>
+        <v>0.132704599321979</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.128171599588515</v>
+        <v>0.89549111678725</v>
       </c>
       <c r="F60" t="n">
-        <v>0.12817922870219</v>
+        <v>0.898153110541741</v>
       </c>
       <c r="G60" t="n">
-        <v>0.898565894390509</v>
+        <v>0.373884537709441</v>
       </c>
     </row>
     <row r="61">
@@ -1957,19 +1954,19 @@
         <v>67</v>
       </c>
       <c r="C61" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0109383029819518</v>
+        <v>-0.147081688202165</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0749922181056738</v>
+        <v>-1.00484476804786</v>
       </c>
       <c r="F61" t="n">
-        <v>0.074993713659636</v>
+        <v>1.00852490920179</v>
       </c>
       <c r="G61" t="n">
-        <v>0.940538008733802</v>
+        <v>0.318478325667224</v>
       </c>
     </row>
     <row r="62">
@@ -1980,19 +1977,19 @@
         <v>68</v>
       </c>
       <c r="C62" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0306988728041998</v>
+        <v>0.103775863792581</v>
       </c>
       <c r="E62" t="n">
-        <v>0.210527020209654</v>
+        <v>0.706385265161956</v>
       </c>
       <c r="F62" t="n">
-        <v>0.210560110067352</v>
+        <v>0.707663031249457</v>
       </c>
       <c r="G62" t="n">
-        <v>0.834140763568952</v>
+        <v>0.482724766485443</v>
       </c>
     </row>
     <row r="63">
@@ -2003,19 +2000,19 @@
         <v>69</v>
       </c>
       <c r="C63" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0688715857680922</v>
+        <v>-0.152905347261831</v>
       </c>
       <c r="E63" t="n">
-        <v>0.472908466773703</v>
+        <v>-1.04525195330558</v>
       </c>
       <c r="F63" t="n">
-        <v>0.473283599960043</v>
+        <v>1.04939452101729</v>
       </c>
       <c r="G63" t="n">
-        <v>0.63820174941071</v>
+        <v>0.29947884420783</v>
       </c>
     </row>
     <row r="64">
@@ -2026,19 +2023,19 @@
         <v>70</v>
       </c>
       <c r="C64" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.0534815224989294</v>
+        <v>-0.195615569923088</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.36700102077931</v>
+        <v>-1.34405145449017</v>
       </c>
       <c r="F64" t="n">
-        <v>0.367176334108407</v>
+        <v>1.3528658254958</v>
       </c>
       <c r="G64" t="n">
-        <v>0.715135620291075</v>
+        <v>0.182710868299005</v>
       </c>
     </row>
     <row r="65">
@@ -2049,19 +2046,19 @@
         <v>71</v>
       </c>
       <c r="C65" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0218449220407598</v>
+        <v>-0.114658548370204</v>
       </c>
       <c r="E65" t="n">
-        <v>0.149785069159389</v>
+        <v>-0.781087068793834</v>
       </c>
       <c r="F65" t="n">
-        <v>0.149796986156391</v>
+        <v>0.782814804302993</v>
       </c>
       <c r="G65" t="n">
-        <v>0.881565768364161</v>
+        <v>0.437747501158506</v>
       </c>
     </row>
     <row r="66">
@@ -2072,19 +2069,19 @@
         <v>72</v>
       </c>
       <c r="C66" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.0109603663451291</v>
+        <v>-0.123612810931784</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.075143495039225</v>
+        <v>-0.842692654761884</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0751449996621451</v>
+        <v>0.844862524989518</v>
       </c>
       <c r="G66" t="n">
-        <v>0.940418285281689</v>
+        <v>0.40256053410415</v>
       </c>
     </row>
     <row r="67">
@@ -2095,19 +2092,19 @@
         <v>73</v>
       </c>
       <c r="C67" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.0491681222704555</v>
+        <v>-0.117537415557364</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.337351688825115</v>
+        <v>-0.800879284610482</v>
       </c>
       <c r="F67" t="n">
-        <v>0.337487849638664</v>
+        <v>0.802741778585761</v>
       </c>
       <c r="G67" t="n">
-        <v>0.737251826673957</v>
+        <v>0.426252222351163</v>
       </c>
     </row>
     <row r="68">
@@ -2118,19 +2115,19 @@
         <v>8</v>
       </c>
       <c r="C68" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0387843132067794</v>
+        <v>-0.163456606231725</v>
       </c>
       <c r="E68" t="n">
-        <v>0.266025295925261</v>
+        <v>-1.11865136723104</v>
       </c>
       <c r="F68" t="n">
-        <v>0.26609206146944</v>
+        <v>1.12373022321313</v>
       </c>
       <c r="G68" t="n">
-        <v>0.791332168279569</v>
+        <v>0.266957850966457</v>
       </c>
     </row>
     <row r="69">
@@ -2141,19 +2138,19 @@
         <v>9</v>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.0863719151835319</v>
+        <v>-0.0508062451603337</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.42419118461863</v>
+        <v>-0.243868166981991</v>
       </c>
       <c r="F69" t="n">
-        <v>0.424721440174613</v>
+        <v>0.243973276586879</v>
       </c>
       <c r="G69" t="n">
-        <v>0.674823234553918</v>
+        <v>0.809414657014439</v>
       </c>
     </row>
     <row r="70">
@@ -2164,19 +2161,19 @@
         <v>10</v>
       </c>
       <c r="C70" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.112881778530315</v>
+        <v>0.273703129840595</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.555372493584126</v>
+        <v>1.34696909589426</v>
       </c>
       <c r="F70" t="n">
-        <v>0.556562829866875</v>
+        <v>1.36474806542822</v>
       </c>
       <c r="G70" t="n">
-        <v>0.582979131533252</v>
+        <v>0.185536051555463</v>
       </c>
     </row>
     <row r="71">
@@ -2187,19 +2184,19 @@
         <v>11</v>
       </c>
       <c r="C71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D71" t="n">
-        <v>0.112881778530315</v>
+        <v>-0.273703129840595</v>
       </c>
       <c r="E71" t="n">
-        <v>0.555372493584125</v>
+        <v>-1.34696909589426</v>
       </c>
       <c r="F71" t="n">
-        <v>0.556562829866874</v>
+        <v>1.36474806542822</v>
       </c>
       <c r="G71" t="n">
-        <v>0.582979131533252</v>
+        <v>0.185536051555462</v>
       </c>
     </row>
     <row r="72">
@@ -2210,19 +2207,19 @@
         <v>12</v>
       </c>
       <c r="C72" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.112881778530315</v>
+        <v>0.273703129840595</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.555372493584126</v>
+        <v>1.34696909589426</v>
       </c>
       <c r="F72" t="n">
-        <v>0.556562829866875</v>
+        <v>1.36474806542822</v>
       </c>
       <c r="G72" t="n">
-        <v>0.582979131533252</v>
+        <v>0.185536051555463</v>
       </c>
     </row>
     <row r="73">
@@ -2233,19 +2230,19 @@
         <v>13</v>
       </c>
       <c r="C73" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0591255754008658</v>
+        <v>-0.268427221635292</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.405817855220105</v>
+        <v>-1.86628118181823</v>
       </c>
       <c r="F73" t="n">
-        <v>0.406054894562472</v>
+        <v>1.88992220045005</v>
       </c>
       <c r="G73" t="n">
-        <v>0.686545132411692</v>
+        <v>0.0650792679325348</v>
       </c>
     </row>
     <row r="74">
@@ -2256,19 +2253,19 @@
         <v>14</v>
       </c>
       <c r="C74" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0236816647551492</v>
+        <v>-0.319303148149148</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.162383674536487</v>
+        <v>-2.24407597334634</v>
       </c>
       <c r="F74" t="n">
-        <v>0.162398858675407</v>
+        <v>2.28524593924076</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8716879718638</v>
+        <v>0.0269564413768025</v>
       </c>
     </row>
     <row r="75">
@@ -2279,19 +2276,19 @@
         <v>15</v>
       </c>
       <c r="C75" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.0565340383871343</v>
+        <v>-0.273040934488135</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.38799154617315</v>
+        <v>-1.9000479872263</v>
       </c>
       <c r="F75" t="n">
-        <v>0.388198697267045</v>
+        <v>1.92499902920781</v>
       </c>
       <c r="G75" t="n">
-        <v>0.69962182531719</v>
+        <v>0.0604261397534834</v>
       </c>
     </row>
     <row r="76">
@@ -2302,19 +2299,19 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.0672726035887321</v>
+        <v>-0.167511384587783</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.461895362214794</v>
+        <v>-1.14692657025163</v>
       </c>
       <c r="F76" t="n">
-        <v>0.462244888841616</v>
+        <v>1.15240074559784</v>
       </c>
       <c r="G76" t="n">
-        <v>0.646038498563629</v>
+        <v>0.255110258789399</v>
       </c>
     </row>
     <row r="77">
@@ -2325,19 +2322,19 @@
         <v>17</v>
       </c>
       <c r="C77" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.0639390470016899</v>
+        <v>-0.173681919558805</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.438942837520845</v>
+        <v>-1.19003182951269</v>
       </c>
       <c r="F77" t="n">
-        <v>0.439242797841027</v>
+        <v>1.19614737421167</v>
       </c>
       <c r="G77" t="n">
-        <v>0.662498522236935</v>
+        <v>0.237768340782027</v>
       </c>
     </row>
     <row r="78">
@@ -2348,19 +2345,19 @@
         <v>18</v>
       </c>
       <c r="C78" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0034147349105787</v>
+        <v>-0.31545687750375</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0234103340905409</v>
+        <v>-2.21506718776251</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0234103795866217</v>
+        <v>2.2546555471261</v>
       </c>
       <c r="G78" t="n">
-        <v>0.981422036597587</v>
+        <v>0.028959200764389</v>
       </c>
     </row>
     <row r="79">
@@ -2371,19 +2368,19 @@
         <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D79" t="n">
-        <v>0.128256421098719</v>
+        <v>0.00827149103275937</v>
       </c>
       <c r="E79" t="n">
-        <v>0.874694750558057</v>
+        <v>0.0554881141505437</v>
       </c>
       <c r="F79" t="n">
-        <v>0.87712148156578</v>
+        <v>0.0554887469085022</v>
       </c>
       <c r="G79" t="n">
-        <v>0.384978666089846</v>
+        <v>0.955994732580245</v>
       </c>
     </row>
     <row r="80">
@@ -2394,19 +2391,19 @@
         <v>20</v>
       </c>
       <c r="C80" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0554080073219123</v>
+        <v>-0.149462911994016</v>
       </c>
       <c r="E80" t="n">
-        <v>0.380247605419932</v>
+        <v>-1.02135806146077</v>
       </c>
       <c r="F80" t="n">
-        <v>0.38044259758293</v>
+        <v>1.02522277587531</v>
       </c>
       <c r="G80" t="n">
-        <v>0.70533093517235</v>
+        <v>0.310619397075556</v>
       </c>
     </row>
     <row r="81">
@@ -2417,19 +2414,19 @@
         <v>21</v>
       </c>
       <c r="C81" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.122156517627768</v>
+        <v>-0.168184898385313</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.841666190619622</v>
+        <v>-1.15162698813953</v>
       </c>
       <c r="F81" t="n">
-        <v>0.843782103706751</v>
+        <v>1.1571688087597</v>
       </c>
       <c r="G81" t="n">
-        <v>0.403065407130387</v>
+        <v>0.253177121956014</v>
       </c>
     </row>
     <row r="82">
@@ -2440,19 +2437,19 @@
         <v>22</v>
       </c>
       <c r="C82" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0200869345536243</v>
+        <v>0.384612048831643</v>
       </c>
       <c r="E82" t="n">
-        <v>0.137727610946272</v>
+        <v>2.74997160764221</v>
       </c>
       <c r="F82" t="n">
-        <v>0.137736875461471</v>
+        <v>2.82594206145036</v>
       </c>
       <c r="G82" t="n">
-        <v>0.891036774930627</v>
+        <v>0.00695228175584623</v>
       </c>
     </row>
     <row r="83">
@@ -2463,19 +2460,19 @@
         <v>23</v>
       </c>
       <c r="C83" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0808953334393758</v>
+        <v>0.0893490083696489</v>
       </c>
       <c r="E83" t="n">
-        <v>0.543850801114044</v>
+        <v>0.594259024838868</v>
       </c>
       <c r="F83" t="n">
-        <v>0.54444676271474</v>
+        <v>0.595054263914086</v>
       </c>
       <c r="G83" t="n">
-        <v>0.58882199604996</v>
+        <v>0.554855361147998</v>
       </c>
     </row>
     <row r="84">
@@ -2486,19 +2483,19 @@
         <v>24</v>
       </c>
       <c r="C84" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00212532204459461</v>
+        <v>0.133848743298118</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0127519514677531</v>
+        <v>0.79664018704305</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0127519610678647</v>
+        <v>0.799049876461196</v>
       </c>
       <c r="G84" t="n">
-        <v>0.989896091697956</v>
+        <v>0.429650872904936</v>
       </c>
     </row>
     <row r="85">
@@ -2509,19 +2506,19 @@
         <v>25</v>
       </c>
       <c r="C85" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.0105362704895295</v>
+        <v>0.199197316094989</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.0666396916113354</v>
+        <v>1.26084364175179</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0666409246880734</v>
+        <v>1.26942691499254</v>
       </c>
       <c r="G85" t="n">
-        <v>0.947199547858427</v>
+        <v>0.211811982505911</v>
       </c>
     </row>
     <row r="86">
@@ -2532,19 +2529,19 @@
         <v>26</v>
       </c>
       <c r="C86" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.00717226046469542</v>
+        <v>0.19209529776385</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.0412022060650472</v>
+        <v>1.10032513838166</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0412025593273832</v>
+        <v>1.10727671658859</v>
       </c>
       <c r="G86" t="n">
-        <v>0.967382696014775</v>
+        <v>0.276428469571535</v>
       </c>
     </row>
     <row r="87">
@@ -2555,19 +2552,19 @@
         <v>27</v>
       </c>
       <c r="C87" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.153930481983514</v>
+        <v>0.242748148954588</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.981342275601777</v>
+        <v>1.54683779645013</v>
       </c>
       <c r="F87" t="n">
-        <v>0.985284788003562</v>
+        <v>1.56270318093747</v>
       </c>
       <c r="G87" t="n">
-        <v>0.330406774974581</v>
+        <v>0.126201491641838</v>
       </c>
     </row>
     <row r="88">
@@ -2581,16 +2578,16 @@
         <v>29</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00759045093655206</v>
+        <v>0.0104733459521726</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0394418975159634</v>
+        <v>0.054423091908782</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0394422762720646</v>
+        <v>0.0544240869406771</v>
       </c>
       <c r="G88" t="n">
-        <v>0.968827980151665</v>
+        <v>0.956998005157147</v>
       </c>
     </row>
     <row r="89">
@@ -2601,19 +2598,19 @@
         <v>29</v>
       </c>
       <c r="C89" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.170708709191612</v>
+        <v>0.121352678452895</v>
       </c>
       <c r="E89" t="n">
-        <v>-1.06272373529386</v>
+        <v>0.741815378247552</v>
       </c>
       <c r="F89" t="n">
-        <v>1.06799568969624</v>
+        <v>0.74365554624367</v>
       </c>
       <c r="G89" t="n">
-        <v>0.292260466818985</v>
+        <v>0.461781408192312</v>
       </c>
     </row>
     <row r="90">
@@ -2624,19 +2621,19 @@
         <v>30</v>
       </c>
       <c r="C90" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.00388425626881253</v>
+        <v>0.0732891814104148</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.0236271273148288</v>
+        <v>0.440524952552482</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0236271867276421</v>
+        <v>0.440920842836271</v>
       </c>
       <c r="G90" t="n">
-        <v>0.98127695364817</v>
+        <v>0.661906966271687</v>
       </c>
     </row>
     <row r="91">
@@ -2647,19 +2644,19 @@
         <v>31</v>
       </c>
       <c r="C91" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0490760240676292</v>
+        <v>0.063873255893197</v>
       </c>
       <c r="E91" t="n">
-        <v>0.32947665776571</v>
+        <v>0.424264847822722</v>
       </c>
       <c r="F91" t="n">
-        <v>0.329609141504047</v>
+        <v>0.424554179547667</v>
       </c>
       <c r="G91" t="n">
-        <v>0.743224712357652</v>
+        <v>0.673230547318162</v>
       </c>
     </row>
     <row r="92">
@@ -2670,19 +2667,19 @@
         <v>32</v>
       </c>
       <c r="C92" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0728171940556232</v>
+        <v>-0.0896917683751664</v>
       </c>
       <c r="E92" t="n">
-        <v>0.461352945558395</v>
+        <v>-0.561634201796787</v>
       </c>
       <c r="F92" t="n">
-        <v>0.46176221017456</v>
+        <v>0.562391593270047</v>
       </c>
       <c r="G92" t="n">
-        <v>0.646753443058948</v>
+        <v>0.577067777141832</v>
       </c>
     </row>
     <row r="93">
@@ -2693,19 +2690,19 @@
         <v>33</v>
       </c>
       <c r="C93" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D93" t="n">
-        <v>0.046264465206197</v>
+        <v>0.233968086381021</v>
       </c>
       <c r="E93" t="n">
-        <v>0.273899797390282</v>
+        <v>1.39000129431443</v>
       </c>
       <c r="F93" t="n">
-        <v>0.273997656752902</v>
+        <v>1.40320358638739</v>
       </c>
       <c r="G93" t="n">
-        <v>0.785697062948842</v>
+        <v>0.169623137321245</v>
       </c>
     </row>
     <row r="94">
@@ -2716,19 +2713,19 @@
         <v>34</v>
       </c>
       <c r="C94" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.00840776513572121</v>
+        <v>0.212006937743104</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.0497421814627207</v>
+        <v>1.25523952541355</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0497427675424797</v>
+        <v>1.2649570555836</v>
       </c>
       <c r="G94" t="n">
-        <v>0.960610166659309</v>
+        <v>0.214488298187354</v>
       </c>
     </row>
     <row r="95">
@@ -2739,19 +2736,19 @@
         <v>35</v>
       </c>
       <c r="C95" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0828838598664189</v>
+        <v>0.198523507172744</v>
       </c>
       <c r="E95" t="n">
-        <v>0.518799728590902</v>
+        <v>1.24024935196517</v>
       </c>
       <c r="F95" t="n">
-        <v>0.51939667208482</v>
+        <v>1.24863373550475</v>
       </c>
       <c r="G95" t="n">
-        <v>0.606419553698904</v>
+        <v>0.219437169201254</v>
       </c>
     </row>
     <row r="96">
@@ -2762,19 +2759,19 @@
         <v>36</v>
       </c>
       <c r="C96" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0637930823862597</v>
+        <v>0.275690072920291</v>
       </c>
       <c r="E96" t="n">
-        <v>0.393781723722879</v>
+        <v>1.72149225872605</v>
       </c>
       <c r="F96" t="n">
-        <v>0.394049591472714</v>
+        <v>1.74456511361027</v>
       </c>
       <c r="G96" t="n">
-        <v>0.695747096192975</v>
+        <v>0.0893632749286467</v>
       </c>
     </row>
     <row r="97">
@@ -2785,19 +2782,19 @@
         <v>37</v>
       </c>
       <c r="C97" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.0334423765472644</v>
+        <v>0.297966514823827</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.189249222578187</v>
+        <v>1.71089881509725</v>
       </c>
       <c r="F97" t="n">
-        <v>0.189284526697921</v>
+        <v>1.73795149003124</v>
       </c>
       <c r="G97" t="n">
-        <v>0.851065309625173</v>
+        <v>0.0921453485062805</v>
       </c>
     </row>
     <row r="98">
@@ -2808,19 +2805,19 @@
         <v>38</v>
       </c>
       <c r="C98" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0399745073044868</v>
+        <v>0.237591261351963</v>
       </c>
       <c r="E98" t="n">
-        <v>0.21906612991709</v>
+        <v>1.30439306857913</v>
       </c>
       <c r="F98" t="n">
-        <v>0.219124540015639</v>
+        <v>1.31718541232583</v>
       </c>
       <c r="G98" t="n">
-        <v>0.828037059404985</v>
+        <v>0.198089798316952</v>
       </c>
     </row>
     <row r="99">
@@ -2831,19 +2828,19 @@
         <v>39</v>
       </c>
       <c r="C99" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.151411689575935</v>
+        <v>0.280576547916269</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.952892604719913</v>
+        <v>1.77724849562638</v>
       </c>
       <c r="F99" t="n">
-        <v>0.95659447813171</v>
+        <v>1.80197224870936</v>
       </c>
       <c r="G99" t="n">
-        <v>0.344664510322868</v>
+        <v>0.0794871844164491</v>
       </c>
     </row>
     <row r="100">
@@ -2854,19 +2851,19 @@
         <v>40</v>
       </c>
       <c r="C100" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.0525737462259069</v>
+        <v>0.369713219809738</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.328625937335186</v>
+        <v>2.39235281145922</v>
       </c>
       <c r="F100" t="n">
-        <v>0.328777624832589</v>
+        <v>2.45286053304726</v>
       </c>
       <c r="G100" t="n">
-        <v>0.744082767524588</v>
+        <v>0.0188745593430152</v>
       </c>
     </row>
     <row r="101">
@@ -2880,16 +2877,16 @@
         <v>28</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0539159784408546</v>
+        <v>0.102159561227095</v>
       </c>
       <c r="E101" t="n">
-        <v>0.275185481742227</v>
+        <v>0.522737214056506</v>
       </c>
       <c r="F101" t="n">
-        <v>0.275319084431517</v>
+        <v>0.52365333723782</v>
       </c>
       <c r="G101" t="n">
-        <v>0.785247331079558</v>
+        <v>0.604954944187661</v>
       </c>
     </row>
     <row r="102">
@@ -2903,16 +2900,16 @@
         <v>28</v>
       </c>
       <c r="D102" t="n">
-        <v>0.00719658616138474</v>
+        <v>-0.0139519058171964</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0366961667854879</v>
+        <v>-0.0711456565552969</v>
       </c>
       <c r="F102" t="n">
-        <v>0.036696483551538</v>
+        <v>0.0711479650283198</v>
       </c>
       <c r="G102" t="n">
-        <v>0.971007316122148</v>
+        <v>0.943824451103993</v>
       </c>
     </row>
     <row r="103">
@@ -2923,19 +2920,19 @@
         <v>43</v>
       </c>
       <c r="C103" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.142648974635917</v>
+        <v>0.156447863802082</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.885385768496953</v>
+        <v>0.959515308970947</v>
       </c>
       <c r="F103" t="n">
-        <v>0.888433036905274</v>
+        <v>0.963499526675156</v>
       </c>
       <c r="G103" t="n">
-        <v>0.379897284536243</v>
+        <v>0.341552125783759</v>
       </c>
     </row>
     <row r="104">
@@ -2946,19 +2943,19 @@
         <v>44</v>
       </c>
       <c r="C104" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00364953105457608</v>
+        <v>0.0794305320991509</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0221993293104767</v>
+        <v>0.477589291688168</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0221993785900429</v>
+        <v>0.478093775891088</v>
       </c>
       <c r="G104" t="n">
-        <v>0.982408203992662</v>
+        <v>0.6354740141092</v>
       </c>
     </row>
     <row r="105">
@@ -2969,19 +2966,19 @@
         <v>45</v>
       </c>
       <c r="C105" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.0392310048429104</v>
+        <v>0.196401608084141</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.20769756257845</v>
+        <v>1.03396688351084</v>
       </c>
       <c r="F105" t="n">
-        <v>0.207750898324323</v>
+        <v>1.04080386879198</v>
       </c>
       <c r="G105" t="n">
-        <v>0.836927155392152</v>
+        <v>0.307197346286521</v>
       </c>
     </row>
     <row r="106">
@@ -2992,19 +2989,19 @@
         <v>46</v>
       </c>
       <c r="C106" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D106" t="n">
-        <v>0.105191546712543</v>
+        <v>-0.00584203930804392</v>
       </c>
       <c r="E106" t="n">
-        <v>0.606523182182166</v>
+        <v>-0.0330479408578856</v>
       </c>
       <c r="F106" t="n">
-        <v>0.607650688769632</v>
+        <v>0.0330481288470107</v>
       </c>
       <c r="G106" t="n">
-        <v>0.547578349410332</v>
+        <v>0.973841487480742</v>
       </c>
     </row>
     <row r="107">
@@ -3015,19 +3012,19 @@
         <v>47</v>
       </c>
       <c r="C107" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.381108279988938</v>
+        <v>0.160910088422289</v>
       </c>
       <c r="E107" t="n">
-        <v>-2.16136612545154</v>
+        <v>0.858921122928319</v>
       </c>
       <c r="F107" t="n">
-        <v>2.21986305157135</v>
+        <v>0.862697911651255</v>
       </c>
       <c r="G107" t="n">
-        <v>0.034404969867955</v>
+        <v>0.395632803156256</v>
       </c>
     </row>
     <row r="108">
@@ -3038,19 +3035,19 @@
         <v>48</v>
       </c>
       <c r="C108" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.123355351169252</v>
+        <v>-0.200515225393681</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.667689390002539</v>
+        <v>-1.07560005954934</v>
       </c>
       <c r="F108" t="n">
-        <v>0.669401406657915</v>
+        <v>1.08302239100895</v>
       </c>
       <c r="G108" t="n">
-        <v>0.508534314428633</v>
+        <v>0.288037163074246</v>
       </c>
     </row>
     <row r="109">
@@ -3064,16 +3061,16 @@
         <v>15</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.208051517844229</v>
+        <v>-0.253819666976106</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.761253891318928</v>
+        <v>-0.935609188309901</v>
       </c>
       <c r="F109" t="n">
-        <v>0.766922309872809</v>
+        <v>0.946144584968867</v>
       </c>
       <c r="G109" t="n">
-        <v>0.456830265987667</v>
+        <v>0.361330220815531</v>
       </c>
     </row>
     <row r="110">
@@ -3087,16 +3084,16 @@
         <v>24</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.00615293011973356</v>
+        <v>0.142486967422813</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.028860164607687</v>
+        <v>0.672901909695334</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0288603467132872</v>
+        <v>0.675212528299888</v>
       </c>
       <c r="G110" t="n">
-        <v>0.977236181638959</v>
+        <v>0.506576053244566</v>
       </c>
     </row>
     <row r="111">
@@ -3107,19 +3104,19 @@
         <v>51</v>
       </c>
       <c r="C111" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0576186402760433</v>
+        <v>0.338504595324755</v>
       </c>
       <c r="E111" t="n">
-        <v>0.299727220325201</v>
+        <v>1.79690788558016</v>
       </c>
       <c r="F111" t="n">
-        <v>0.299893460426244</v>
+        <v>1.83433179430894</v>
       </c>
       <c r="G111" t="n">
-        <v>0.766555147196882</v>
+        <v>0.0780741523716491</v>
       </c>
     </row>
     <row r="112">
@@ -3130,19 +3127,19 @@
         <v>52</v>
       </c>
       <c r="C112" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D112" t="n">
-        <v>0.166655297828053</v>
+        <v>-0.00115725277657463</v>
       </c>
       <c r="E112" t="n">
-        <v>0.966375746199355</v>
+        <v>-0.0065464132092971</v>
       </c>
       <c r="F112" t="n">
-        <v>0.97094018479301</v>
+        <v>0.00654641467049505</v>
       </c>
       <c r="G112" t="n">
-        <v>0.338641330118817</v>
+        <v>0.994817396309753</v>
       </c>
     </row>
     <row r="113">
@@ -3153,19 +3150,19 @@
         <v>53</v>
       </c>
       <c r="C113" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.165698691444191</v>
+        <v>0.0507355590149335</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.869007916522381</v>
+        <v>0.258923923249595</v>
       </c>
       <c r="F113" t="n">
-        <v>0.873064528907529</v>
+        <v>0.259035211145156</v>
       </c>
       <c r="G113" t="n">
-        <v>0.390326716724681</v>
+        <v>0.797647952135748</v>
       </c>
     </row>
     <row r="114">
@@ -3176,19 +3173,19 @@
         <v>54</v>
       </c>
       <c r="C114" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.0454291367751421</v>
+        <v>0.0112946303410266</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.236219312294262</v>
+        <v>0.0575939896540044</v>
       </c>
       <c r="F114" t="n">
-        <v>0.236300684495513</v>
+        <v>0.0575952142974547</v>
       </c>
       <c r="G114" t="n">
-        <v>0.814982822516793</v>
+        <v>0.95451142798687</v>
       </c>
     </row>
     <row r="115">
@@ -3202,16 +3199,16 @@
         <v>15</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.181746330630892</v>
+        <v>-0.124931434041875</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.66265735862</v>
+        <v>-0.452812388727335</v>
       </c>
       <c r="F115" t="n">
-        <v>0.666394210847604</v>
+        <v>0.454003638365968</v>
       </c>
       <c r="G115" t="n">
-        <v>0.516811567074575</v>
+        <v>0.657313120067997</v>
       </c>
     </row>
     <row r="116">
@@ -3225,16 +3222,16 @@
         <v>23</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.0598626928035614</v>
+        <v>0.114478931797117</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.274653712885054</v>
+        <v>0.526918300088863</v>
       </c>
       <c r="F116" t="n">
-        <v>0.274818174245966</v>
+        <v>0.528080140261463</v>
       </c>
       <c r="G116" t="n">
-        <v>0.786141510934738</v>
+        <v>0.602979949882301</v>
       </c>
     </row>
     <row r="117">
@@ -3245,19 +3242,19 @@
         <v>57</v>
       </c>
       <c r="C117" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0971679457112141</v>
+        <v>0.151614843852238</v>
       </c>
       <c r="E117" t="n">
-        <v>0.600879319520614</v>
+        <v>0.929402690308741</v>
       </c>
       <c r="F117" t="n">
-        <v>0.601831311400319</v>
+        <v>0.933023166799955</v>
       </c>
       <c r="G117" t="n">
-        <v>0.550860558840217</v>
+        <v>0.356857017712221</v>
       </c>
     </row>
     <row r="118">
@@ -3268,19 +3265,19 @@
         <v>58</v>
       </c>
       <c r="C118" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.00563820272170393</v>
+        <v>0.272388860232371</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.0342962116747496</v>
+        <v>1.67665394427962</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0342963933878209</v>
+        <v>1.69856039683948</v>
       </c>
       <c r="G118" t="n">
-        <v>0.972825158745749</v>
+        <v>0.0980303407258968</v>
       </c>
     </row>
     <row r="119">
@@ -3291,19 +3288,19 @@
         <v>59</v>
       </c>
       <c r="C119" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.197585914172877</v>
+        <v>-0.0444598053235072</v>
       </c>
       <c r="E119" t="n">
-        <v>-1.2013148406296</v>
+        <v>-0.263201268002036</v>
       </c>
       <c r="F119" t="n">
-        <v>1.20935726947839</v>
+        <v>0.263288101563995</v>
       </c>
       <c r="G119" t="n">
-        <v>0.234408079854416</v>
+        <v>0.793872394884087</v>
       </c>
     </row>
     <row r="120">
@@ -3314,19 +3311,19 @@
         <v>60</v>
       </c>
       <c r="C120" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.0834920923467709</v>
+        <v>-0.0381315272403255</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.495098458127219</v>
+        <v>-0.222450958407133</v>
       </c>
       <c r="F120" t="n">
-        <v>0.495676564164094</v>
+        <v>0.222504922425355</v>
       </c>
       <c r="G120" t="n">
-        <v>0.623220822726355</v>
+        <v>0.82525209721577</v>
       </c>
     </row>
     <row r="121">
@@ -3337,19 +3334,19 @@
         <v>61</v>
       </c>
       <c r="C121" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.0310575321780085</v>
+        <v>0.247513911324034</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.212988211678125</v>
+        <v>1.71432027377459</v>
       </c>
       <c r="F121" t="n">
-        <v>0.213022475716812</v>
+        <v>1.73263304322438</v>
       </c>
       <c r="G121" t="n">
-        <v>0.832230735097566</v>
+        <v>0.0898614702626411</v>
       </c>
     </row>
     <row r="122">
@@ -3360,19 +3357,19 @@
         <v>62</v>
       </c>
       <c r="C122" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D122" t="n">
-        <v>0.194335006218329</v>
+        <v>0.094592890070797</v>
       </c>
       <c r="E122" t="n">
-        <v>1.21339343146584</v>
+        <v>0.577111509519023</v>
       </c>
       <c r="F122" t="n">
-        <v>1.22124418562225</v>
+        <v>0.577977716534589</v>
       </c>
       <c r="G122" t="n">
-        <v>0.22951665728394</v>
+        <v>0.566780434112246</v>
       </c>
     </row>
     <row r="123">
@@ -3383,19 +3380,19 @@
         <v>63</v>
       </c>
       <c r="C123" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D123" t="n">
-        <v>0.20349591305746</v>
+        <v>0.110699745541483</v>
       </c>
       <c r="E123" t="n">
-        <v>1.27219203849798</v>
+        <v>0.676131216440057</v>
       </c>
       <c r="F123" t="n">
-        <v>1.28124202614454</v>
+        <v>0.677524399804733</v>
       </c>
       <c r="G123" t="n">
-        <v>0.207872501316047</v>
+        <v>0.502288138820928</v>
       </c>
     </row>
     <row r="124">
@@ -3409,16 +3406,16 @@
         <v>40</v>
       </c>
       <c r="D124" t="n">
-        <v>0.18423260304324</v>
+        <v>0.31680129479545</v>
       </c>
       <c r="E124" t="n">
-        <v>1.14880324449237</v>
+        <v>2.02246738241373</v>
       </c>
       <c r="F124" t="n">
-        <v>1.15546450225877</v>
+        <v>2.05894671090837</v>
       </c>
       <c r="G124" t="n">
-        <v>0.255114078037193</v>
+        <v>0.0464012486625138</v>
       </c>
     </row>
     <row r="125">
@@ -3432,16 +3429,16 @@
         <v>40</v>
       </c>
       <c r="D125" t="n">
-        <v>0.314863358010737</v>
+        <v>0.351338021151531</v>
       </c>
       <c r="E125" t="n">
-        <v>2.00919745581417</v>
+        <v>2.26215118525719</v>
       </c>
       <c r="F125" t="n">
-        <v>2.04496091766125</v>
+        <v>2.31326682597534</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0478296753287468</v>
+        <v>0.0262158891522254</v>
       </c>
     </row>
     <row r="126">
@@ -3452,19 +3449,19 @@
         <v>66</v>
       </c>
       <c r="C126" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D126" t="n">
-        <v>0.183844242053283</v>
+        <v>-0.0106692988167936</v>
       </c>
       <c r="E126" t="n">
-        <v>1.26123203864058</v>
+        <v>-0.07157454823315</v>
       </c>
       <c r="F126" t="n">
-        <v>1.26851363796546</v>
+        <v>0.0715759062793805</v>
       </c>
       <c r="G126" t="n">
-        <v>0.210996734095884</v>
+        <v>0.943256587525217</v>
       </c>
     </row>
     <row r="127">
@@ -3475,19 +3472,19 @@
         <v>67</v>
       </c>
       <c r="C127" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.19150293220327</v>
+        <v>0.024328364582913</v>
       </c>
       <c r="E127" t="n">
-        <v>-1.32928984946093</v>
+        <v>0.16503556152037</v>
       </c>
       <c r="F127" t="n">
-        <v>1.33763484880814</v>
+        <v>0.165051848343525</v>
       </c>
       <c r="G127" t="n">
-        <v>0.187452559576571</v>
+        <v>0.869626381825283</v>
       </c>
     </row>
     <row r="128">
@@ -3498,19 +3495,19 @@
         <v>68</v>
       </c>
       <c r="C128" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D128" t="n">
-        <v>0.0659370337204704</v>
+        <v>-0.069874900915029</v>
       </c>
       <c r="E128" t="n">
-        <v>0.452698355332717</v>
+        <v>-0.474688199317693</v>
       </c>
       <c r="F128" t="n">
-        <v>0.453027413234983</v>
+        <v>0.475075833968579</v>
       </c>
       <c r="G128" t="n">
-        <v>0.652613550356663</v>
+        <v>0.636980949906523</v>
       </c>
     </row>
     <row r="129">
@@ -3521,19 +3518,19 @@
         <v>69</v>
       </c>
       <c r="C129" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.181501436450104</v>
+        <v>0.18463282820934</v>
       </c>
       <c r="E129" t="n">
-        <v>-1.2582514378912</v>
+        <v>1.26676841640738</v>
       </c>
       <c r="F129" t="n">
-        <v>1.26532738584229</v>
+        <v>1.27414644070969</v>
       </c>
       <c r="G129" t="n">
-        <v>0.211991250929369</v>
+        <v>0.209011276979313</v>
       </c>
     </row>
     <row r="130">
@@ -3544,19 +3541,19 @@
         <v>70</v>
       </c>
       <c r="C130" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.212765077049005</v>
+        <v>0.181445473402011</v>
       </c>
       <c r="E130" t="n">
-        <v>-1.48127219035872</v>
+        <v>1.24440133090611</v>
       </c>
       <c r="F130" t="n">
-        <v>1.49282450961918</v>
+        <v>1.25139497116953</v>
       </c>
       <c r="G130" t="n">
-        <v>0.142166066596634</v>
+        <v>0.217117173414832</v>
       </c>
     </row>
     <row r="131">
@@ -3567,19 +3564,19 @@
         <v>71</v>
       </c>
       <c r="C131" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.16309571646637</v>
+        <v>0.0611617505207028</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.12820334659967</v>
+        <v>0.415337584711611</v>
       </c>
       <c r="F131" t="n">
-        <v>1.13330253545113</v>
+        <v>0.415597227371413</v>
       </c>
       <c r="G131" t="n">
-        <v>0.262835295864726</v>
+        <v>0.679637137670054</v>
       </c>
     </row>
     <row r="132">
@@ -3590,19 +3587,19 @@
         <v>72</v>
       </c>
       <c r="C132" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.175149176711413</v>
+        <v>-0.0578721319057509</v>
       </c>
       <c r="E132" t="n">
-        <v>-1.21327202661795</v>
+        <v>-0.392946971753884</v>
       </c>
       <c r="F132" t="n">
-        <v>1.21961518448352</v>
+        <v>0.393166841586473</v>
       </c>
       <c r="G132" t="n">
-        <v>0.228695864950472</v>
+        <v>0.696012558482208</v>
       </c>
     </row>
     <row r="133">
@@ -3613,1537 +3610,19 @@
         <v>73</v>
       </c>
       <c r="C133" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.161846020573996</v>
+        <v>0.00645779599449758</v>
       </c>
       <c r="E133" t="n">
-        <v>-1.11940357630871</v>
+        <v>0.0437995122640635</v>
       </c>
       <c r="F133" t="n">
-        <v>1.12438427051338</v>
+        <v>0.0437998167026146</v>
       </c>
       <c r="G133" t="n">
-        <v>0.266559887388189</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>75</v>
-      </c>
-      <c r="B134" t="s">
-        <v>8</v>
-      </c>
-      <c r="C134" t="n">
-        <v>49</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-0.184209787141666</v>
-      </c>
-      <c r="E134" t="n">
-        <v>-1.2774612714898</v>
-      </c>
-      <c r="F134" t="n">
-        <v>1.2848666635241</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0.205135199226984</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>75</v>
-      </c>
-      <c r="B135" t="s">
-        <v>9</v>
-      </c>
-      <c r="C135" t="n">
-        <v>26</v>
-      </c>
-      <c r="D135" t="n">
-        <v>0.00491212053715395</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0.0240645712941624</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0.0240646680712214</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0.980999996501113</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>75</v>
-      </c>
-      <c r="B136" t="s">
-        <v>10</v>
-      </c>
-      <c r="C136" t="n">
-        <v>26</v>
-      </c>
-      <c r="D136" t="n">
-        <v>0.163488230077256</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0.808177973227911</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0.811848678168079</v>
-      </c>
-      <c r="G136" t="n">
-        <v>0.424857808691996</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>75</v>
-      </c>
-      <c r="B137" t="s">
-        <v>11</v>
-      </c>
-      <c r="C137" t="n">
-        <v>26</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-0.163488230077256</v>
-      </c>
-      <c r="E137" t="n">
-        <v>-0.808177973227912</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0.81184867816808</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0.424857808691996</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>75</v>
-      </c>
-      <c r="B138" t="s">
-        <v>12</v>
-      </c>
-      <c r="C138" t="n">
-        <v>26</v>
-      </c>
-      <c r="D138" t="n">
-        <v>0.163488230077256</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0.808177973227911</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0.811848678168079</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0.424857808691996</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>75</v>
-      </c>
-      <c r="B139" t="s">
-        <v>13</v>
-      </c>
-      <c r="C139" t="n">
-        <v>49</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-0.289596496959242</v>
-      </c>
-      <c r="E139" t="n">
-        <v>-2.0438472813114</v>
-      </c>
-      <c r="F139" t="n">
-        <v>2.07425795172838</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0.0435578519910627</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>75</v>
-      </c>
-      <c r="B140" t="s">
-        <v>14</v>
-      </c>
-      <c r="C140" t="n">
-        <v>49</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-0.343308299740866</v>
-      </c>
-      <c r="E140" t="n">
-        <v>-2.45321399179374</v>
-      </c>
-      <c r="F140" t="n">
-        <v>2.5059050952855</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0.0157342481900357</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>75</v>
-      </c>
-      <c r="B141" t="s">
-        <v>15</v>
-      </c>
-      <c r="C141" t="n">
-        <v>49</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-0.294423257782205</v>
-      </c>
-      <c r="E141" t="n">
-        <v>-2.08002264790872</v>
-      </c>
-      <c r="F141" t="n">
-        <v>2.11208192833259</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0.0400220292268944</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>75</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>49</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-0.189353461569184</v>
-      </c>
-      <c r="E142" t="n">
-        <v>-1.31399933611843</v>
-      </c>
-      <c r="F142" t="n">
-        <v>1.32205931691957</v>
-      </c>
-      <c r="G142" t="n">
-        <v>0.192546818764939</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>75</v>
-      </c>
-      <c r="B143" t="s">
-        <v>17</v>
-      </c>
-      <c r="C143" t="n">
-        <v>49</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-0.195935767568797</v>
-      </c>
-      <c r="E143" t="n">
-        <v>-1.36086481709526</v>
-      </c>
-      <c r="F143" t="n">
-        <v>1.3698195253513</v>
-      </c>
-      <c r="G143" t="n">
-        <v>0.177252269196845</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>75</v>
-      </c>
-      <c r="B144" t="s">
-        <v>18</v>
-      </c>
-      <c r="C144" t="n">
-        <v>49</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-0.339702579541532</v>
-      </c>
-      <c r="E144" t="n">
-        <v>-2.42523080728728</v>
-      </c>
-      <c r="F144" t="n">
-        <v>2.47613190770841</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0.0169392323229818</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>75</v>
-      </c>
-      <c r="B145" t="s">
-        <v>19</v>
-      </c>
-      <c r="C145" t="n">
-        <v>48</v>
-      </c>
-      <c r="D145" t="n">
-        <v>0.0261961799770801</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0.177711795315236</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.177732130802785</v>
-      </c>
-      <c r="G145" t="n">
-        <v>0.859713711426029</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>75</v>
-      </c>
-      <c r="B146" t="s">
-        <v>20</v>
-      </c>
-      <c r="C146" t="n">
-        <v>49</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-0.165330008106051</v>
-      </c>
-      <c r="E146" t="n">
-        <v>-1.14394538325432</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1.14926121638848</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.256263236650522</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>75</v>
-      </c>
-      <c r="B147" t="s">
-        <v>21</v>
-      </c>
-      <c r="C147" t="n">
-        <v>49</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-0.152309993603897</v>
-      </c>
-      <c r="E147" t="n">
-        <v>-1.05237344173739</v>
-      </c>
-      <c r="F147" t="n">
-        <v>1.05651126744125</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.29613516024991</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>75</v>
-      </c>
-      <c r="B148" t="s">
-        <v>22</v>
-      </c>
-      <c r="C148" t="n">
-        <v>49</v>
-      </c>
-      <c r="D148" t="n">
-        <v>0.380895545901273</v>
-      </c>
-      <c r="E148" t="n">
-        <v>2.74984936677008</v>
-      </c>
-      <c r="F148" t="n">
-        <v>2.82418046373089</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0.00693288739143081</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>75</v>
-      </c>
-      <c r="B149" t="s">
-        <v>23</v>
-      </c>
-      <c r="C149" t="n">
-        <v>47</v>
-      </c>
-      <c r="D149" t="n">
-        <v>0.0722609237381424</v>
-      </c>
-      <c r="E149" t="n">
-        <v>0.485587380561796</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0.486011562520574</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.629317325105894</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>75</v>
-      </c>
-      <c r="B150" t="s">
-        <v>24</v>
-      </c>
-      <c r="C150" t="n">
-        <v>38</v>
-      </c>
-      <c r="D150" t="n">
-        <v>0.116079875037361</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0.699633032448084</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0.701219577518274</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0.487674310576316</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>75</v>
-      </c>
-      <c r="B151" t="s">
-        <v>25</v>
-      </c>
-      <c r="C151" t="n">
-        <v>42</v>
-      </c>
-      <c r="D151" t="n">
-        <v>0.180849367996702</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1.15651221180747</v>
-      </c>
-      <c r="F151" t="n">
-        <v>1.16296824114639</v>
-      </c>
-      <c r="G151" t="n">
-        <v>0.251733621549304</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>75</v>
-      </c>
-      <c r="B152" t="s">
-        <v>26</v>
-      </c>
-      <c r="C152" t="n">
-        <v>35</v>
-      </c>
-      <c r="D152" t="n">
-        <v>0.171391556650708</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0.994383697111747</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0.999357028794207</v>
-      </c>
-      <c r="G152" t="n">
-        <v>0.324893730888489</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>75</v>
-      </c>
-      <c r="B153" t="s">
-        <v>27</v>
-      </c>
-      <c r="C153" t="n">
-        <v>42</v>
-      </c>
-      <c r="D153" t="n">
-        <v>0.223839456096717</v>
-      </c>
-      <c r="E153" t="n">
-        <v>1.44006616378911</v>
-      </c>
-      <c r="F153" t="n">
-        <v>1.45254177471537</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0.154150965288114</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>75</v>
-      </c>
-      <c r="B154" t="s">
-        <v>28</v>
-      </c>
-      <c r="C154" t="n">
-        <v>29</v>
-      </c>
-      <c r="D154" t="n">
-        <v>0.0078382070258839</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0.0407293525439436</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0.0407297696138346</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0.967811022541356</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>75</v>
-      </c>
-      <c r="B155" t="s">
-        <v>29</v>
-      </c>
-      <c r="C155" t="n">
-        <v>40</v>
-      </c>
-      <c r="D155" t="n">
-        <v>0.0986817900277387</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0.610301637738105</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0.61129913474192</v>
-      </c>
-      <c r="G155" t="n">
-        <v>0.544641406748866</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>75</v>
-      </c>
-      <c r="B156" t="s">
-        <v>30</v>
-      </c>
-      <c r="C156" t="n">
-        <v>39</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0.0441324420998494</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0.268621651508532</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.268708971245371</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0.789646306515692</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>75</v>
-      </c>
-      <c r="B157" t="s">
-        <v>31</v>
-      </c>
-      <c r="C157" t="n">
-        <v>47</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0.0453521202015197</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0.30444011133211</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.304544628245719</v>
-      </c>
-      <c r="G157" t="n">
-        <v>0.762117005986939</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>75</v>
-      </c>
-      <c r="B158" t="s">
-        <v>32</v>
-      </c>
-      <c r="C158" t="n">
-        <v>42</v>
-      </c>
-      <c r="D158" t="n">
-        <v>-0.116332287834933</v>
-      </c>
-      <c r="E158" t="n">
-        <v>-0.739096220948471</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0.74077962453247</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0.463153730472816</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>75</v>
-      </c>
-      <c r="B159" t="s">
-        <v>33</v>
-      </c>
-      <c r="C159" t="n">
-        <v>37</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0.213098363023663</v>
-      </c>
-      <c r="E159" t="n">
-        <v>1.28032763875545</v>
-      </c>
-      <c r="F159" t="n">
-        <v>1.29034517745014</v>
-      </c>
-      <c r="G159" t="n">
-        <v>0.205390702066743</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>75</v>
-      </c>
-      <c r="B160" t="s">
-        <v>34</v>
-      </c>
-      <c r="C160" t="n">
-        <v>37</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0.19434574913188</v>
-      </c>
-      <c r="E160" t="n">
-        <v>1.16457776980475</v>
-      </c>
-      <c r="F160" t="n">
-        <v>1.1721135390947</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0.249068328630093</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>75</v>
-      </c>
-      <c r="B161" t="s">
-        <v>35</v>
-      </c>
-      <c r="C161" t="n">
-        <v>41</v>
-      </c>
-      <c r="D161" t="n">
-        <v>0.189794521315197</v>
-      </c>
-      <c r="E161" t="n">
-        <v>1.19981401776402</v>
-      </c>
-      <c r="F161" t="n">
-        <v>1.20720883471556</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0.234622676662271</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>75</v>
-      </c>
-      <c r="B162" t="s">
-        <v>36</v>
-      </c>
-      <c r="C162" t="n">
-        <v>40</v>
-      </c>
-      <c r="D162" t="n">
-        <v>0.264583576562402</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1.67074500218132</v>
-      </c>
-      <c r="F162" t="n">
-        <v>1.69127508195059</v>
-      </c>
-      <c r="G162" t="n">
-        <v>0.0989713039106636</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>75</v>
-      </c>
-      <c r="B163" t="s">
-        <v>37</v>
-      </c>
-      <c r="C163" t="n">
-        <v>34</v>
-      </c>
-      <c r="D163" t="n">
-        <v>0.289133275939564</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1.68359417448843</v>
-      </c>
-      <c r="F163" t="n">
-        <v>1.7085593287209</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0.0972167281599845</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>75</v>
-      </c>
-      <c r="B164" t="s">
-        <v>38</v>
-      </c>
-      <c r="C164" t="n">
-        <v>32</v>
-      </c>
-      <c r="D164" t="n">
-        <v>0.226101707669001</v>
-      </c>
-      <c r="E164" t="n">
-        <v>1.26018530549485</v>
-      </c>
-      <c r="F164" t="n">
-        <v>1.27133287367238</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0.213379169395302</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>75</v>
-      </c>
-      <c r="B165" t="s">
-        <v>39</v>
-      </c>
-      <c r="C165" t="n">
-        <v>41</v>
-      </c>
-      <c r="D165" t="n">
-        <v>0.26223388478767</v>
-      </c>
-      <c r="E165" t="n">
-        <v>1.67681786284521</v>
-      </c>
-      <c r="F165" t="n">
-        <v>1.69703907630558</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0.0976574899732531</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>75</v>
-      </c>
-      <c r="B166" t="s">
-        <v>40</v>
-      </c>
-      <c r="C166" t="n">
-        <v>41</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0.332425056806155</v>
-      </c>
-      <c r="E166" t="n">
-        <v>2.15797233986966</v>
-      </c>
-      <c r="F166" t="n">
-        <v>2.20117537602356</v>
-      </c>
-      <c r="G166" t="n">
-        <v>0.0337087456032187</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>75</v>
-      </c>
-      <c r="B167" t="s">
-        <v>41</v>
-      </c>
-      <c r="C167" t="n">
-        <v>28</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0.090889990768666</v>
-      </c>
-      <c r="E167" t="n">
-        <v>0.464732384503776</v>
-      </c>
-      <c r="F167" t="n">
-        <v>0.465376056463258</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0.645536754850071</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>75</v>
-      </c>
-      <c r="B168" t="s">
-        <v>42</v>
-      </c>
-      <c r="C168" t="n">
-        <v>28</v>
-      </c>
-      <c r="D168" t="n">
-        <v>-0.0474419184464782</v>
-      </c>
-      <c r="E168" t="n">
-        <v>-0.24208900317557</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0.242179962983711</v>
-      </c>
-      <c r="G168" t="n">
-        <v>0.810540839126836</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>75</v>
-      </c>
-      <c r="B169" t="s">
-        <v>43</v>
-      </c>
-      <c r="C169" t="n">
-        <v>40</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0.136284360591609</v>
-      </c>
-      <c r="E169" t="n">
-        <v>0.845373224727488</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.848025502417361</v>
-      </c>
-      <c r="G169" t="n">
-        <v>0.401733939284588</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>75</v>
-      </c>
-      <c r="B170" t="s">
-        <v>44</v>
-      </c>
-      <c r="C170" t="n">
-        <v>39</v>
-      </c>
-      <c r="D170" t="n">
-        <v>0.0498058180398864</v>
-      </c>
-      <c r="E170" t="n">
-        <v>0.30320784425836</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0.303333424778836</v>
-      </c>
-      <c r="G170" t="n">
-        <v>0.763334887729422</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>75</v>
-      </c>
-      <c r="B171" t="s">
-        <v>45</v>
-      </c>
-      <c r="C171" t="n">
-        <v>30</v>
-      </c>
-      <c r="D171" t="n">
-        <v>0.196494370137321</v>
-      </c>
-      <c r="E171" t="n">
-        <v>1.05345088934989</v>
-      </c>
-      <c r="F171" t="n">
-        <v>1.06042348060045</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0.298013927978158</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>75</v>
-      </c>
-      <c r="B172" t="s">
-        <v>46</v>
-      </c>
-      <c r="C172" t="n">
-        <v>35</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0.0247316627853605</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0.142101563334768</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0.142116055880005</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.887852458218409</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>75</v>
-      </c>
-      <c r="B173" t="s">
-        <v>47</v>
-      </c>
-      <c r="C173" t="n">
-        <v>31</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0.174232717656542</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0.947943058675536</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.952846153960245</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0.348543071950051</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>75</v>
-      </c>
-      <c r="B174" t="s">
-        <v>48</v>
-      </c>
-      <c r="C174" t="n">
-        <v>31</v>
-      </c>
-      <c r="D174" t="n">
-        <v>-0.189706901905491</v>
-      </c>
-      <c r="E174" t="n">
-        <v>-1.03412995421684</v>
-      </c>
-      <c r="F174" t="n">
-        <v>1.04049756981622</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0.306706277880087</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>75</v>
-      </c>
-      <c r="B175" t="s">
-        <v>49</v>
-      </c>
-      <c r="C175" t="n">
-        <v>15</v>
-      </c>
-      <c r="D175" t="n">
-        <v>-0.218350718262905</v>
-      </c>
-      <c r="E175" t="n">
-        <v>-0.800156922159998</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.806741080803803</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0.434327292035967</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>75</v>
-      </c>
-      <c r="B176" t="s">
-        <v>50</v>
-      </c>
-      <c r="C176" t="n">
-        <v>24</v>
-      </c>
-      <c r="D176" t="n">
-        <v>0.101167869045526</v>
-      </c>
-      <c r="E176" t="n">
-        <v>0.476148274235838</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0.476966506286661</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0.638089769271355</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>75</v>
-      </c>
-      <c r="B177" t="s">
-        <v>51</v>
-      </c>
-      <c r="C177" t="n">
-        <v>29</v>
-      </c>
-      <c r="D177" t="n">
-        <v>0.334440754696111</v>
-      </c>
-      <c r="E177" t="n">
-        <v>1.80732551510664</v>
-      </c>
-      <c r="F177" t="n">
-        <v>1.84398790445068</v>
-      </c>
-      <c r="G177" t="n">
-        <v>0.0761856403614807</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>75</v>
-      </c>
-      <c r="B178" t="s">
-        <v>52</v>
-      </c>
-      <c r="C178" t="n">
-        <v>35</v>
-      </c>
-      <c r="D178" t="n">
-        <v>0.0145274010171075</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0.0834594368074776</v>
-      </c>
-      <c r="F178" t="n">
-        <v>0.0834623728729938</v>
-      </c>
-      <c r="G178" t="n">
-        <v>0.933988139822859</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>75</v>
-      </c>
-      <c r="B179" t="s">
-        <v>53</v>
-      </c>
-      <c r="C179" t="n">
-        <v>29</v>
-      </c>
-      <c r="D179" t="n">
-        <v>0.0552658488060558</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0.287462680021509</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0.287609334677246</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0.775841834532175</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>75</v>
-      </c>
-      <c r="B180" t="s">
-        <v>54</v>
-      </c>
-      <c r="C180" t="n">
-        <v>29</v>
-      </c>
-      <c r="D180" t="n">
-        <v>0.00916958352072195</v>
-      </c>
-      <c r="E180" t="n">
-        <v>0.0476478890879016</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0.0476485568439139</v>
-      </c>
-      <c r="G180" t="n">
-        <v>0.962347042492019</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>75</v>
-      </c>
-      <c r="B181" t="s">
-        <v>55</v>
-      </c>
-      <c r="C181" t="n">
-        <v>15</v>
-      </c>
-      <c r="D181" t="n">
-        <v>-0.112467334498916</v>
-      </c>
-      <c r="E181" t="n">
-        <v>-0.407229573790859</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0.408095937653026</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0.689844896350303</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>75</v>
-      </c>
-      <c r="B182" t="s">
-        <v>56</v>
-      </c>
-      <c r="C182" t="n">
-        <v>23</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0.0445245060502514</v>
-      </c>
-      <c r="E182" t="n">
-        <v>0.204171909605782</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.204239465077661</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0.840132769545683</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>75</v>
-      </c>
-      <c r="B183" t="s">
-        <v>57</v>
-      </c>
-      <c r="C183" t="n">
-        <v>40</v>
-      </c>
-      <c r="D183" t="n">
-        <v>0.156185075187824</v>
-      </c>
-      <c r="E183" t="n">
-        <v>0.970734773231259</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.974751806060177</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0.335848000257978</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>75</v>
-      </c>
-      <c r="B184" t="s">
-        <v>58</v>
-      </c>
-      <c r="C184" t="n">
-        <v>39</v>
-      </c>
-      <c r="D184" t="n">
-        <v>0.289005668069678</v>
-      </c>
-      <c r="E184" t="n">
-        <v>1.80950610505514</v>
-      </c>
-      <c r="F184" t="n">
-        <v>1.83631313032699</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0.0743563678258463</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>75</v>
-      </c>
-      <c r="B185" t="s">
-        <v>59</v>
-      </c>
-      <c r="C185" t="n">
-        <v>38</v>
-      </c>
-      <c r="D185" t="n">
-        <v>-0.0306530019531516</v>
-      </c>
-      <c r="E185" t="n">
-        <v>-0.18397564773703</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0.184004477939134</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0.855042504655905</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>75</v>
-      </c>
-      <c r="B186" t="s">
-        <v>60</v>
-      </c>
-      <c r="C186" t="n">
-        <v>37</v>
-      </c>
-      <c r="D186" t="n">
-        <v>-0.0637395421141134</v>
-      </c>
-      <c r="E186" t="n">
-        <v>-0.377600134041723</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.377856562124292</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0.707819087243172</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>75</v>
-      </c>
-      <c r="B187" t="s">
-        <v>61</v>
-      </c>
-      <c r="C187" t="n">
-        <v>49</v>
-      </c>
-      <c r="D187" t="n">
-        <v>0.255932791215005</v>
-      </c>
-      <c r="E187" t="n">
-        <v>1.79447605933334</v>
-      </c>
-      <c r="F187" t="n">
-        <v>1.81503740491053</v>
-      </c>
-      <c r="G187" t="n">
-        <v>0.0759021967481357</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>75</v>
-      </c>
-      <c r="B188" t="s">
-        <v>62</v>
-      </c>
-      <c r="C188" t="n">
-        <v>40</v>
-      </c>
-      <c r="D188" t="n">
-        <v>0.1233665808624</v>
-      </c>
-      <c r="E188" t="n">
-        <v>0.764376303918758</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.766336595471777</v>
-      </c>
-      <c r="G188" t="n">
-        <v>0.448210699678982</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>75</v>
-      </c>
-      <c r="B189" t="s">
-        <v>63</v>
-      </c>
-      <c r="C189" t="n">
-        <v>40</v>
-      </c>
-      <c r="D189" t="n">
-        <v>0.131528298109944</v>
-      </c>
-      <c r="E189" t="n">
-        <v>0.815519522278224</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.817900461336366</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.418513231892052</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>75</v>
-      </c>
-      <c r="B190" t="s">
-        <v>64</v>
-      </c>
-      <c r="C190" t="n">
-        <v>40</v>
-      </c>
-      <c r="D190" t="n">
-        <v>0.325467183354719</v>
-      </c>
-      <c r="E190" t="n">
-        <v>2.08203064373734</v>
-      </c>
-      <c r="F190" t="n">
-        <v>2.1218416610578</v>
-      </c>
-      <c r="G190" t="n">
-        <v>0.0404294918734522</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>75</v>
-      </c>
-      <c r="B191" t="s">
-        <v>65</v>
-      </c>
-      <c r="C191" t="n">
-        <v>40</v>
-      </c>
-      <c r="D191" t="n">
-        <v>0.352005055148041</v>
-      </c>
-      <c r="E191" t="n">
-        <v>2.26684335310577</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2.3182791648972</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0.0259131163672555</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>75</v>
-      </c>
-      <c r="B192" t="s">
-        <v>66</v>
-      </c>
-      <c r="C192" t="n">
-        <v>48</v>
-      </c>
-      <c r="D192" t="n">
-        <v>-0.0381606631358983</v>
-      </c>
-      <c r="E192" t="n">
-        <v>-0.258943953131111</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0.259006866058223</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.796785502013503</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>75</v>
-      </c>
-      <c r="B193" t="s">
-        <v>67</v>
-      </c>
-      <c r="C193" t="n">
-        <v>49</v>
-      </c>
-      <c r="D193" t="n">
-        <v>0.0302622911827654</v>
-      </c>
-      <c r="E193" t="n">
-        <v>0.207531184031284</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0.207562881229953</v>
-      </c>
-      <c r="G193" t="n">
-        <v>0.83646704194617</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>75</v>
-      </c>
-      <c r="B194" t="s">
-        <v>68</v>
-      </c>
-      <c r="C194" t="n">
-        <v>49</v>
-      </c>
-      <c r="D194" t="n">
-        <v>-0.0619547088471894</v>
-      </c>
-      <c r="E194" t="n">
-        <v>-0.425284778514076</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0.425557597111471</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0.672372610086835</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>75</v>
-      </c>
-      <c r="B195" t="s">
-        <v>69</v>
-      </c>
-      <c r="C195" t="n">
-        <v>49</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0.179066366696383</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1.24099660971404</v>
-      </c>
-      <c r="F195" t="n">
-        <v>1.24778511540335</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0.218290902659472</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>75</v>
-      </c>
-      <c r="B196" t="s">
-        <v>70</v>
-      </c>
-      <c r="C196" t="n">
-        <v>49</v>
-      </c>
-      <c r="D196" t="n">
-        <v>0.176441960327132</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1.22241753968142</v>
-      </c>
-      <c r="F196" t="n">
-        <v>1.22890537735676</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0.225224840724122</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>75</v>
-      </c>
-      <c r="B197" t="s">
-        <v>71</v>
-      </c>
-      <c r="C197" t="n">
-        <v>49</v>
-      </c>
-      <c r="D197" t="n">
-        <v>0.0645663357831243</v>
-      </c>
-      <c r="E197" t="n">
-        <v>0.443261140603525</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.443570042551606</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0.659388800140496</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>75</v>
-      </c>
-      <c r="B198" t="s">
-        <v>72</v>
-      </c>
-      <c r="C198" t="n">
-        <v>49</v>
-      </c>
-      <c r="D198" t="n">
-        <v>-0.0474796988825315</v>
-      </c>
-      <c r="E198" t="n">
-        <v>-0.325749344678239</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0.325871933414865</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0.74596774126247</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>75</v>
-      </c>
-      <c r="B199" t="s">
-        <v>73</v>
-      </c>
-      <c r="C199" t="n">
-        <v>49</v>
-      </c>
-      <c r="D199" t="n">
-        <v>0.0145380293586423</v>
-      </c>
-      <c r="E199" t="n">
-        <v>0.0996747304767167</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.0996782421224133</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0.921023733909183</v>
+        <v>0.965253554336515</v>
       </c>
     </row>
   </sheetData>
@@ -5185,45 +3664,45 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>0.346905454726616</v>
+        <v>-0.395589783045375</v>
       </c>
       <c r="E2" t="n">
-        <v>2.42784349659265</v>
+        <v>-2.21401563814101</v>
       </c>
       <c r="F2" t="n">
-        <v>2.48119445253468</v>
+        <v>2.27918350394534</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0168974109969343</v>
+        <v>0.0304790566043085</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>0.290555550987982</v>
+        <v>-0.319303148149148</v>
       </c>
       <c r="E3" t="n">
-        <v>2.00691304819843</v>
+        <v>-2.24407597334634</v>
       </c>
       <c r="F3" t="n">
-        <v>2.03698525244695</v>
+        <v>2.28524593924076</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0475594739120552</v>
+        <v>0.0269564413768025</v>
       </c>
     </row>
     <row r="4">
@@ -5231,22 +3710,22 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.381108279988938</v>
+        <v>-0.31545687750375</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.16136612545154</v>
+        <v>-2.21506718776251</v>
       </c>
       <c r="F4" t="n">
-        <v>2.21986305157135</v>
+        <v>2.2546555471261</v>
       </c>
       <c r="G4" t="n">
-        <v>0.034404969867955</v>
+        <v>0.028959200764389</v>
       </c>
     </row>
     <row r="5">
@@ -5254,206 +3733,91 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>0.314863358010737</v>
+        <v>0.384612048831643</v>
       </c>
       <c r="E5" t="n">
-        <v>2.00919745581417</v>
+        <v>2.74997160764221</v>
       </c>
       <c r="F5" t="n">
-        <v>2.04496091766125</v>
+        <v>2.82594206145036</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0478296753287468</v>
+        <v>0.00695228175584623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.289596496959242</v>
+        <v>0.369713219809738</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0438472813114</v>
+        <v>2.39235281145922</v>
       </c>
       <c r="F6" t="n">
-        <v>2.07425795172838</v>
+        <v>2.45286053304726</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0435578519910627</v>
+        <v>0.0188745593430152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.343308299740866</v>
+        <v>0.31680129479545</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.45321399179374</v>
+        <v>2.02246738241373</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5059050952855</v>
+        <v>2.05894671090837</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0157342481900357</v>
+        <v>0.0464012486625138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.294423257782205</v>
+        <v>0.351338021151531</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.08002264790872</v>
+        <v>2.26215118525719</v>
       </c>
       <c r="F8" t="n">
-        <v>2.11208192833259</v>
+        <v>2.31326682597534</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0400220292268944</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="n">
-        <v>49</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.339702579541532</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-2.42523080728728</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.47613190770841</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0169392323229818</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="n">
-        <v>49</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.380895545901273</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.74984936677008</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.82418046373089</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.00693288739143081</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="n">
-        <v>41</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.332425056806155</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.15797233986966</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.20117537602356</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0337087456032187</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="n">
-        <v>40</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.325467183354719</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.08203064373734</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.1218416610578</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0404294918734522</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="n">
-        <v>40</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.352005055148041</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.26684335310577</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.3182791648972</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0259131163672555</v>
+        <v>0.0262158891522254</v>
       </c>
     </row>
   </sheetData>
